--- a/MIS/III BSC-  (CS) studentsList.xlsx
+++ b/MIS/III BSC-  (CS) studentsList.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CSA OFFICE 2023 Onwards\NAME LIST\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\MIS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4545"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
   </bookViews>
   <sheets>
-    <sheet name="I BSC" sheetId="2" r:id="rId1"/>
+    <sheet name="III BSC" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'I BSC'!$A$1:$C$59</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'I BSC'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'III BSC'!$A$1:$C$59</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'III BSC'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -298,9 +298,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -312,6 +309,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -603,665 +603,665 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6">
+      <c r="A2" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>112348001</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="5">
         <v>112348002</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="5">
         <v>112348003</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>112348004</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="5">
         <v>112348005</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="5">
         <v>112348006</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="5">
         <v>112348007</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>112348008</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>112348009</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="5">
         <v>112348010</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="5">
         <v>112348011</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>112348012</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="5">
         <v>112348013</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="5">
         <v>112348014</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>112348016</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="5">
         <v>112348017</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="5">
         <v>112348019</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>112348021</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>112348022</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="5">
         <v>112348024</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="6">
+      <c r="B22" s="5">
         <v>112348025</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>112348026</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="6">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="6">
+      <c r="B24" s="5">
         <v>112348028</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>112348029</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="6">
+      <c r="B26" s="5">
         <v>112348030</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>112348031</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="5">
         <v>112348032</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>112348033</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="6">
+      <c r="B30" s="5">
         <v>112348034</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>112348035</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="6">
+      <c r="B32" s="5">
         <v>112348036</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>112348037</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="6">
+      <c r="B34" s="5">
         <v>112348038</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>112348041</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>112348042</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="6">
+      <c r="B37" s="5">
         <v>112348043</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="6" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="6">
+      <c r="B38" s="5">
         <v>112348044</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="6" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="5">
         <v>112348045</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="6" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="6">
+      <c r="B40" s="5">
         <v>112348046</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="6">
+      <c r="B41" s="5">
         <v>112348047</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6">
+      <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="6">
+      <c r="B42" s="5">
         <v>112348048</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="6" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="6">
+      <c r="B43" s="5">
         <v>112348049</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
+      <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="6">
+      <c r="B44" s="5">
         <v>112348050</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="6" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6">
+      <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="6">
+      <c r="B45" s="5">
         <v>112348051</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="6">
+      <c r="B46" s="5">
         <v>112348052</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="6" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="6">
+      <c r="B47" s="5">
         <v>112348053</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="6">
+      <c r="B48" s="5">
         <v>112348054</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="6">
+      <c r="B49" s="5">
         <v>112348056</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="6">
+      <c r="B50" s="5">
         <v>112348057</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="6">
+      <c r="B51" s="5">
         <v>112348058</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="6">
+      <c r="B52" s="5">
         <v>112348059</v>
       </c>
-      <c r="C52" s="7" t="s">
+      <c r="C52" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="6">
+      <c r="B53" s="5">
         <v>112348060</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="6">
+      <c r="B54" s="5">
         <v>112348061</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C54" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="6">
+      <c r="B55" s="5">
         <v>112348062</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C55" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="6">
+      <c r="B56" s="5">
         <v>112348064</v>
       </c>
-      <c r="C56" s="7" t="s">
+      <c r="C56" s="6" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
+      <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="6">
+      <c r="B57" s="5">
         <v>112348065</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="6">
+      <c r="B58" s="5">
         <v>112348066</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="6">
+      <c r="B59" s="5">
         <v>112348067</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="6" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C63" s="4"/>
+      <c r="C63" s="8"/>
     </row>
     <row r="64" spans="1:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C64" s="4"/>
+      <c r="C64" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
